--- a/public/exports-from-60-with-coowners/29208654.xlsx
+++ b/public/exports-from-60-with-coowners/29208654.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352257</t>
+          <t xml:space="preserve">311352258</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352250</t>
+          <t xml:space="preserve">311352251</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352299</t>
+          <t xml:space="preserve">311352302</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352303</t>
+          <t xml:space="preserve">311352309</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M103" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29208654.xlsx
+++ b/public/exports-from-60-with-coowners/29208654.xlsx
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352258</t>
+          <t xml:space="preserve">311352260</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352302</t>
+          <t xml:space="preserve">311352299</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29208654.xlsx
+++ b/public/exports-from-60-with-coowners/29208654.xlsx
@@ -3589,7 +3589,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352260</t>
+          <t xml:space="preserve">311352257</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352251</t>
+          <t xml:space="preserve">311352250</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352309</t>
+          <t xml:space="preserve">311352303</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
